--- a/bin/Release/net8.0/Files/KALYAN MORNING PENAL.xlsx
+++ b/bin/Release/net8.0/Files/KALYAN MORNING PENAL.xlsx
@@ -15041,22 +15041,22 @@
         <x:v>521</x:v>
       </x:c>
       <x:c r="B192" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C192" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="D192" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E192" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F192" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G192" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H192" s="3" t="s">
         <x:v>522</x:v>
